--- a/data/Tonor/Mar/business_report.xlsx
+++ b/data/Tonor/Mar/business_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\buybox\data\Tonor\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94F9A02-58D8-43C1-9BE8-DC68F64B280B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F3DA3F-BAD3-439D-9203-3CCE8B03F2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$W$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$W$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="115">
   <si>
     <t>(Parent) ASIN</t>
   </si>
@@ -367,6 +367,18 @@
   </si>
   <si>
     <t>TM310</t>
+  </si>
+  <si>
+    <t>B0DTYHXMRQ</t>
+  </si>
+  <si>
+    <t>TONOR TM20, G11 &amp; TM310 PC Microphone Variation</t>
+  </si>
+  <si>
+    <t>B0FGCSSCB3</t>
+  </si>
+  <si>
+    <t>TONOR TC30S, TC30+ &amp; TC30S+ Microphone Variation</t>
   </si>
 </sst>
 </file>
@@ -735,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -867,7 +879,7 @@
       <c r="S2" s="2">
         <v>0</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="3">
         <v>3218.6440677966102</v>
       </c>
       <c r="U2" s="3">
@@ -938,7 +950,7 @@
       <c r="S3" s="2">
         <v>0</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="3">
         <v>3388.9830508474579</v>
       </c>
       <c r="U3" s="3">
@@ -1009,7 +1021,7 @@
       <c r="S4" s="2">
         <v>0</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="3">
         <v>0</v>
       </c>
       <c r="U4" s="3">
@@ -1080,7 +1092,7 @@
       <c r="S5" s="2">
         <v>3.2300000000000002E-2</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="3">
         <v>40815.254237288136</v>
       </c>
       <c r="U5" s="3">
@@ -1151,7 +1163,7 @@
       <c r="S6" s="2">
         <v>0</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="3">
         <v>22872.881355932204</v>
       </c>
       <c r="U6" s="3">
@@ -1222,7 +1234,7 @@
       <c r="S7" s="2">
         <v>0</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="3">
         <v>9698.3050847457635</v>
       </c>
       <c r="U7" s="3">
@@ -1293,7 +1305,7 @@
       <c r="S8" s="2">
         <v>0</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="3">
         <v>12452.542372881357</v>
       </c>
       <c r="U8" s="3">
@@ -1364,7 +1376,7 @@
       <c r="S9" s="2">
         <v>0</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="3">
         <v>20842.372881355932</v>
       </c>
       <c r="U9" s="3">
@@ -1435,7 +1447,7 @@
       <c r="S10" s="2">
         <v>5.2600000000000001E-2</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="3">
         <v>7624.5762711864409</v>
       </c>
       <c r="U10" s="3">
@@ -1506,7 +1518,7 @@
       <c r="S11" s="2">
         <v>0</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="3">
         <v>6353.3898305084749</v>
       </c>
       <c r="U11" s="3">
@@ -1577,7 +1589,7 @@
       <c r="S12" s="2">
         <v>0</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="3">
         <v>3430.5084745762715</v>
       </c>
       <c r="U12" s="3">
@@ -1648,7 +1660,7 @@
       <c r="S13" s="2">
         <v>0</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="3">
         <v>2244.9152542372881</v>
       </c>
       <c r="U13" s="3">
@@ -1719,7 +1731,7 @@
       <c r="S14" s="2">
         <v>0</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="3">
         <v>2541.5254237288136</v>
       </c>
       <c r="U14" s="3">
@@ -1790,7 +1802,7 @@
       <c r="S15" s="2">
         <v>0</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="3">
         <v>3388.9830508474579</v>
       </c>
       <c r="U15" s="3">
@@ -1861,7 +1873,7 @@
       <c r="S16" s="2">
         <v>0</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="3">
         <v>1609.3220338983051</v>
       </c>
       <c r="U16" s="3">
@@ -1932,7 +1944,7 @@
       <c r="S17" s="2">
         <v>0</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="3">
         <v>0</v>
       </c>
       <c r="U17" s="3">
@@ -2003,7 +2015,7 @@
       <c r="S18" s="2">
         <v>0</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="3">
         <v>0</v>
       </c>
       <c r="U18" s="3">
@@ -2074,7 +2086,7 @@
       <c r="S19" s="2">
         <v>0</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="3">
         <v>0</v>
       </c>
       <c r="U19" s="3">
@@ -2145,7 +2157,7 @@
       <c r="S20" s="2">
         <v>0</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
@@ -2216,7 +2228,7 @@
       <c r="S21" s="2">
         <v>0</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="3">
         <v>0</v>
       </c>
       <c r="U21" s="3">
@@ -2287,7 +2299,7 @@
       <c r="S22" s="2">
         <v>0</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="3">
         <v>0</v>
       </c>
       <c r="U22" s="3">
@@ -2358,7 +2370,7 @@
       <c r="S23" s="2">
         <v>0</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="3">
         <v>0</v>
       </c>
       <c r="U23" s="3">
@@ -2429,7 +2441,7 @@
       <c r="S24" s="2">
         <v>0</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
@@ -2500,7 +2512,7 @@
       <c r="S25" s="2">
         <v>0</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="3">
         <v>0</v>
       </c>
       <c r="U25" s="3">
@@ -2571,7 +2583,7 @@
       <c r="S26" s="2">
         <v>0</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="3">
         <v>0</v>
       </c>
       <c r="U26" s="3">
@@ -2581,6 +2593,148 @@
         <v>0</v>
       </c>
       <c r="W26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C28" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" t="s">
+        <v>114</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
         <v>0</v>
       </c>
     </row>
